--- a/data/data_preparation/smartband/df_alt_cleaned.xlsx
+++ b/data/data_preparation/smartband/df_alt_cleaned.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         <v>185</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="F2" t="n">
         <v>40.64</v>
@@ -540,7 +540,7 @@
         <v>142</v>
       </c>
       <c r="E3" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F3" t="n">
         <v>40.64</v>
@@ -559,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0131</v>
+        <v>0.0126</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -581,10 +581,10 @@
         <v>142</v>
       </c>
       <c r="E4" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F4" t="n">
-        <v>28.829</v>
+        <v>30.099</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0131</v>
+        <v>0.0126</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -611,7 +611,7 @@
         <v>16597584</v>
       </c>
       <c r="B5" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>468</v>
       </c>
       <c r="F5" t="n">
-        <v>33.756</v>
+        <v>30.099</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0535</v>
+        <v>0.054</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>16219140</v>
       </c>
       <c r="B6" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>468</v>
       </c>
       <c r="F6" t="n">
-        <v>28.829</v>
+        <v>30.099</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0131</v>
+        <v>0.0126</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -737,7 +737,7 @@
         <v>240</v>
       </c>
       <c r="E8" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F8" t="n">
         <v>40.64</v>
@@ -756,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0131</v>
+        <v>0.0126</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>296</v>
       </c>
       <c r="E9" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F9" t="n">
         <v>40.64</v>
@@ -797,7 +797,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0399</v>
+        <v>0.0384</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -808,7 +808,7 @@
         <v>18533917</v>
       </c>
       <c r="B10" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         <v>296</v>
       </c>
       <c r="E10" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F10" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -890,7 +890,7 @@
         <v>468</v>
       </c>
       <c r="F12" t="n">
-        <v>33.756</v>
+        <v>30.099</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         <v>240</v>
       </c>
       <c r="E13" t="n">
-        <v>276</v>
+        <v>168</v>
       </c>
       <c r="F13" t="n">
-        <v>37.211</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0275</v>
+        <v>0.0384</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -956,7 +956,7 @@
         <v>18628977</v>
       </c>
       <c r="B14" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="F14" t="n">
         <v>43.22499999999999</v>
@@ -1000,10 +1000,10 @@
         <v>185</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="F15" t="n">
-        <v>37.211</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>468</v>
       </c>
       <c r="F16" t="n">
-        <v>33.756</v>
+        <v>30.099</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0535</v>
+        <v>0.054</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1069,7 +1069,7 @@
         <v>18517515</v>
       </c>
       <c r="B17" t="n">
-        <v>7995</v>
+        <v>7930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>28.829</v>
+        <v>30.099</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1102,7 +1102,7 @@
         <v>17232987</v>
       </c>
       <c r="B18" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>468</v>
       </c>
       <c r="F18" t="n">
-        <v>28.829</v>
+        <v>30.099</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0275</v>
+        <v>0.0247</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1154,7 +1154,7 @@
         <v>142</v>
       </c>
       <c r="E19" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F19" t="n">
         <v>40.64</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0131</v>
+        <v>0.0247</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1195,10 +1195,10 @@
         <v>240</v>
       </c>
       <c r="E20" t="n">
-        <v>276</v>
+        <v>168</v>
       </c>
       <c r="F20" t="n">
-        <v>37.211</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0399</v>
+        <v>0.0384</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1222,61 +1222,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18362373</v>
-      </c>
-      <c r="B21" t="inlineStr"/>
+        <v>17353248</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3385</v>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Nictom</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>240</v>
-      </c>
-      <c r="E21" t="n">
-        <v>29</v>
-      </c>
-      <c r="F21" t="n">
-        <v>28.829</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SAMOLED</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>0.0535</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17353248</v>
+        <v>15905518</v>
       </c>
       <c r="B22" t="n">
-        <v>3385</v>
+        <v>17689.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nictom</t>
+          <t>Amazfit</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>375</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="E22" t="n">
+        <v>288</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Silicona</t>
@@ -1285,152 +1285,150 @@
       <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15905518</v>
+        <v>811935548</v>
       </c>
       <c r="B23" t="n">
-        <v>17689.5</v>
+        <v>1495</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Amazfit</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>240</v>
-      </c>
-      <c r="E23" t="n">
-        <v>276</v>
-      </c>
-      <c r="F23" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.0275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>811935548</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1495</v>
-      </c>
+        <v>18362367</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mia</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>240</v>
+      </c>
+      <c r="E24" t="n">
+        <v>56</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30.099</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SAMOLED</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>18577715</v>
-      </c>
-      <c r="B25" t="inlineStr"/>
+        <v>18628975</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5012.5</v>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>29</v>
-      </c>
+          <t>Microwear</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>375</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>52.479</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LTPO OLED</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Fluoroelastómero</t>
-        </is>
-      </c>
+          <t>LCD IPS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.0399</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>18362367</v>
-      </c>
-      <c r="B26" t="inlineStr"/>
+        <v>16999363</v>
+      </c>
+      <c r="B26" t="n">
+        <v>17689.5</v>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Amazfit</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>240</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="F26" t="n">
-        <v>28.829</v>
+        <v>40.64</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SAMOLED</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0275</v>
+        <v>0.0247</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1438,43 +1436,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18628975</v>
+        <v>17944054</v>
       </c>
       <c r="B27" t="n">
-        <v>5012.5</v>
+        <v>10660.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Microwear</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>375</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>185</v>
+      </c>
+      <c r="E27" t="n">
+        <v>288</v>
+      </c>
       <c r="F27" t="n">
-        <v>43.22499999999999</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LCD IPS</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.0126</v>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16999363</v>
+        <v>16649900</v>
       </c>
       <c r="B28" t="n">
-        <v>17689.5</v>
+        <v>7930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1485,26 +1491,26 @@
         <v>240</v>
       </c>
       <c r="E28" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="F28" t="n">
-        <v>40.64</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AMOLED</t>
+          <t>LCD TFT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Caucho de silicona</t>
         </is>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0275</v>
+        <v>0.0384</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1512,40 +1518,36 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>17944054</v>
+        <v>870551279</v>
       </c>
       <c r="B29" t="n">
-        <v>10660.5</v>
+        <v>5012.5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="E29" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F29" t="n">
-        <v>37.211</v>
+        <v>30.099</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>AMOLED</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0131</v>
+        <v>0.0126</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1553,40 +1555,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16649900</v>
+        <v>798823809</v>
       </c>
       <c r="B30" t="n">
-        <v>7995</v>
+        <v>3385</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Amazfit</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>240</v>
-      </c>
-      <c r="E30" t="n">
-        <v>276</v>
-      </c>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>37.211</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>LCD TFT</t>
-        </is>
-      </c>
+        <v>19.335</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Caucho de silicona</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0275</v>
+        <v>0.0247</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1594,36 +1588,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>870551279</v>
+        <v>1129376761</v>
       </c>
       <c r="B31" t="n">
-        <v>5012.5</v>
+        <v>7930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Kospet</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>142</v>
-      </c>
-      <c r="E31" t="n">
-        <v>276</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>28.829</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>43.22499999999999</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0131</v>
+        <v>0.054</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1631,36 +1623,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>18347134</v>
-      </c>
-      <c r="B32" t="inlineStr"/>
+        <v>925659331</v>
+      </c>
+      <c r="B32" t="n">
+        <v>10660.5</v>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>296</v>
+      </c>
       <c r="E32" t="n">
-        <v>276</v>
-      </c>
-      <c r="F32" t="n">
-        <v>19.208</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LCD MIP</t>
+          <t>Táctil</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0399</v>
+        <v>0.0126</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1668,20 +1662,22 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>798823809</v>
+        <v>1130385828</v>
       </c>
       <c r="B33" t="n">
-        <v>3385</v>
+        <v>1495</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>BlueStar</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>142</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>19.208</v>
+        <v>34.163</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
@@ -1690,10 +1686,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0275</v>
+        <v>0.0247</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1701,24 +1697,30 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1129376761</v>
+        <v>18582027</v>
       </c>
       <c r="B34" t="n">
-        <v>7995</v>
+        <v>5012.5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>Colmi</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>375</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>185</v>
+      </c>
+      <c r="E34" t="n">
+        <v>168</v>
+      </c>
       <c r="F34" t="n">
         <v>43.22499999999999</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LCD IPS</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Silicona</t>
@@ -1728,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0535</v>
+        <v>0.0384</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1736,10 +1738,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>925659331</v>
+        <v>19146618</v>
       </c>
       <c r="B35" t="n">
-        <v>10660.5</v>
+        <v>7930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1747,27 +1749,29 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="E35" t="n">
-        <v>468</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>288</v>
+      </c>
+      <c r="F35" t="n">
+        <v>37.33799999999999</v>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Táctil</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0131</v>
+        <v>0.0126</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1775,22 +1779,20 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1130385828</v>
+        <v>1114447581</v>
       </c>
       <c r="B36" t="n">
-        <v>1495</v>
+        <v>3385</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BlueStar</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>142</v>
-      </c>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>33.756</v>
+        <v>19.335</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
@@ -1799,10 +1801,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0275</v>
+        <v>0.0126</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1810,40 +1812,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18582027</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5012.5</v>
-      </c>
+        <v>15906639</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Colmi</t>
+          <t>Amazfit</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>185</v>
+        <v>375</v>
       </c>
       <c r="E37" t="n">
-        <v>120</v>
+        <v>468</v>
       </c>
       <c r="F37" t="n">
-        <v>43.22499999999999</v>
+        <v>34.163</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LCD IPS</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Cuero</t>
         </is>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0399</v>
+        <v>0.054</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1851,24 +1851,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>19146618</v>
+        <v>15974482</v>
       </c>
       <c r="B38" t="n">
-        <v>7995</v>
+        <v>10660.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>185</v>
+        <v>82.5</v>
       </c>
       <c r="E38" t="n">
-        <v>276</v>
+        <v>168</v>
       </c>
       <c r="F38" t="n">
-        <v>37.211</v>
+        <v>19.335</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1877,47 +1877,41 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Caucho de silicona</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="n">
-        <v>0.0131</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1114447581</v>
+        <v>18554971</v>
       </c>
       <c r="B39" t="n">
-        <v>3385</v>
+        <v>7930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Shirajo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>19.208</v>
-      </c>
+      <c r="E39" t="n">
+        <v>168</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0131</v>
+        <v>0.0247</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1925,22 +1919,24 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>15906639</v>
-      </c>
-      <c r="B40" t="inlineStr"/>
+        <v>899400867</v>
+      </c>
+      <c r="B40" t="n">
+        <v>6444.5</v>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Amazfit</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>375</v>
+        <v>142</v>
       </c>
       <c r="E40" t="n">
         <v>468</v>
       </c>
       <c r="F40" t="n">
-        <v>37.211</v>
+        <v>30.099</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1949,39 +1945,35 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cuero</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="n">
-        <v>0.0535</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15974482</v>
-      </c>
-      <c r="B41" t="n">
-        <v>10660.5</v>
-      </c>
+        <v>1113448743</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Amazfit</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>82.5</v>
+        <v>375</v>
       </c>
       <c r="E41" t="n">
-        <v>120</v>
+        <v>468</v>
       </c>
       <c r="F41" t="n">
-        <v>19.208</v>
+        <v>34.163</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1990,109 +1982,107 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Caucho de silicona</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>0.054</v>
+      </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>18554971</v>
+        <v>1130594835</v>
       </c>
       <c r="B42" t="n">
-        <v>7995</v>
+        <v>17689.5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shirajo</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
-        <v>120</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>142</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>19.335</v>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.0275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>899400867</v>
+        <v>931473181</v>
       </c>
       <c r="B43" t="n">
-        <v>6455</v>
+        <v>3385</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Belmotec</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>142</v>
-      </c>
-      <c r="E43" t="n">
-        <v>468</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>28.829</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+        <v>52.479</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.0126</v>
+      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1113448743</v>
-      </c>
-      <c r="B44" t="inlineStr"/>
+        <v>809300742</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7930</v>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Amazfit</t>
+          <t>Kingwear</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>375</v>
-      </c>
-      <c r="E44" t="n">
-        <v>468</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>37.211</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+        <v>37.33799999999999</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Silicona</t>
@@ -2101,31 +2091,29 @@
       <c r="I44" t="n">
         <v>1</v>
       </c>
-      <c r="J44" t="n">
-        <v>0.0535</v>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1130594835</v>
+        <v>912006408</v>
       </c>
       <c r="B45" t="n">
-        <v>17689.5</v>
+        <v>1495</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>SmartWatches</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>142</v>
+        <v>82.5</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>19.208</v>
+        <v>34.163</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
@@ -2143,18 +2131,18 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>931473181</v>
+        <v>1120397775</v>
       </c>
       <c r="B46" t="n">
-        <v>3385</v>
+        <v>7930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belmotec</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>82.5</v>
+        <v>375</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
@@ -2169,31 +2157,27 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="J46" t="n">
-        <v>0.0131</v>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>809300742</v>
+        <v>918271731</v>
       </c>
       <c r="B47" t="n">
-        <v>7995</v>
+        <v>1495</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kingwear</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>240</v>
-      </c>
+          <t>PSP_BAND</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>37.211</v>
+        <v>30.099</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
@@ -2206,32 +2190,38 @@
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>912006408</v>
+        <v>1123066687</v>
       </c>
       <c r="B48" t="n">
-        <v>1495</v>
+        <v>17689.5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SmartWatches</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>185</v>
+      </c>
+      <c r="E48" t="n">
+        <v>168</v>
+      </c>
       <c r="F48" t="n">
-        <v>33.756</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>30.099</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2244,53 +2234,61 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1120397775</v>
+        <v>18728650</v>
       </c>
       <c r="B49" t="n">
-        <v>7995</v>
+        <v>7930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
+          <t>Gadnic</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>375</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
+        <v>82.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>288</v>
+      </c>
       <c r="F49" t="n">
-        <v>52.479</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>19.335</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.054</v>
+      </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>918271731</v>
+        <v>1117186349</v>
       </c>
       <c r="B50" t="n">
-        <v>1495</v>
+        <v>3385</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PSP_BAND</t>
+          <t>Goufit</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>28.829</v>
+        <v>19.335</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
@@ -2303,42 +2301,38 @@
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1123066687</v>
+        <v>1123490995</v>
       </c>
       <c r="B51" t="n">
-        <v>17689.5</v>
+        <v>5012.5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
+          <t>Netmak</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="E51" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="F51" t="n">
-        <v>28.829</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
+        <v>34.163</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
@@ -2347,77 +2341,63 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>18507562</v>
+        <v>1139787088</v>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
-        <v>29</v>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>LTPO OLED</t>
-        </is>
-      </c>
+        <v>37.33799999999999</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Caucho</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
-      <c r="J52" t="n">
-        <v>0.0275</v>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>18728650</v>
-      </c>
-      <c r="B53" t="n">
-        <v>7995</v>
-      </c>
+        <v>18592587</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gadnic</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>276</v>
-      </c>
+          <t>Honor</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>19.208</v>
+        <v>34.163</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0535</v>
+        <v>0.0384</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
@@ -2425,22 +2405,30 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1117186349</v>
+        <v>19111235</v>
       </c>
       <c r="B54" t="n">
-        <v>3385</v>
+        <v>17689.5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Goufit</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>375</v>
+      </c>
+      <c r="E54" t="n">
+        <v>288</v>
+      </c>
       <c r="F54" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
+        <v>34.163</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Silicona</t>
@@ -2449,69 +2437,61 @@
       <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>0.0384</v>
+      </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1123490995</v>
+        <v>16656739</v>
       </c>
       <c r="B55" t="n">
-        <v>5012.5</v>
+        <v>1495</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netmak</t>
+          <t>Noga</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>142</v>
-      </c>
-      <c r="E55" t="n">
-        <v>120</v>
-      </c>
-      <c r="F55" t="n">
-        <v>33.756</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1139787088</v>
-      </c>
-      <c r="B56" t="inlineStr"/>
+        <v>761823849</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1495</v>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Nictom</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
-        <v>37.211</v>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>Plástico</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
@@ -2520,34 +2500,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>18592587</v>
-      </c>
-      <c r="B57" t="inlineStr"/>
+        <v>1122496212</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6444.5</v>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Honor</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Microwear</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>240</v>
+      </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>37.211</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+        <v>43.22499999999999</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I57" t="n">
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0399</v>
+        <v>0.054</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
@@ -2555,40 +2535,40 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19111235</v>
+        <v>903582249</v>
       </c>
       <c r="B58" t="n">
-        <v>17689.5</v>
+        <v>6444.5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>375</v>
+        <v>142</v>
       </c>
       <c r="E58" t="n">
-        <v>276</v>
+        <v>468</v>
       </c>
       <c r="F58" t="n">
-        <v>33.756</v>
+        <v>30.099</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Plástico</t>
         </is>
       </c>
       <c r="I58" t="n">
         <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0399</v>
+        <v>0.0126</v>
       </c>
       <c r="K58" t="n">
         <v>1</v>
@@ -2596,24 +2576,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>16656739</v>
+        <v>1116399707</v>
       </c>
       <c r="B59" t="n">
-        <v>1495</v>
+        <v>10660.5</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Noga</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>82.5</v>
+        <v>296</v>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>34.163</v>
+      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Acero inoxidable</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>0</v>
@@ -2621,88 +2609,86 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>761823849</v>
+        <v>1124466025</v>
       </c>
       <c r="B60" t="n">
         <v>1495</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nictom</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>82.5</v>
+      </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>19.335</v>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1122496212</v>
+        <v>905237295</v>
       </c>
       <c r="B61" t="n">
-        <v>6455</v>
+        <v>5012.5</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Microwear</t>
+          <t>Daikon</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>43.22499999999999</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.0535</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>903582249</v>
+        <v>1117044965</v>
       </c>
       <c r="B62" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Mibro</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="E62" t="n">
-        <v>468</v>
+        <v>288</v>
       </c>
       <c r="F62" t="n">
-        <v>28.829</v>
+        <v>30.099</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2711,46 +2697,44 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="I62" t="n">
         <v>1</v>
       </c>
-      <c r="J62" t="n">
-        <v>0.0131</v>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1116399707</v>
+        <v>1127626522</v>
       </c>
       <c r="B63" t="n">
-        <v>10660.5</v>
+        <v>7930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>296</v>
+        <v>375</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>37.211</v>
+        <v>30.099</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
@@ -2759,24 +2743,28 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1124466025</v>
-      </c>
-      <c r="B64" t="n">
-        <v>1495</v>
-      </c>
+        <v>1125121096</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>375</v>
+      </c>
+      <c r="E64" t="n">
+        <v>288</v>
+      </c>
       <c r="F64" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
+        <v>34.163</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Silicona</t>
@@ -2792,62 +2780,58 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>905237295</v>
+        <v>822208885</v>
       </c>
       <c r="B65" t="n">
-        <v>5012.5</v>
+        <v>3385</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Daikon</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>185</v>
-      </c>
+          <t>Daza</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>37.211</v>
+        <v>19.335</v>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1117044965</v>
+        <v>929882638</v>
       </c>
       <c r="B66" t="n">
-        <v>6455</v>
+        <v>10660.5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mibro</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>240</v>
-      </c>
-      <c r="E66" t="n">
-        <v>276</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>33.756</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+        <v>30.099</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -2855,15 +2839,15 @@
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1127626522</v>
+        <v>886371185</v>
       </c>
       <c r="B67" t="n">
-        <v>7995</v>
+        <v>7930</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2871,11 +2855,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>375</v>
+        <v>185</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>33.756</v>
+        <v>40.64</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
@@ -2883,9 +2867,7 @@
           <t>Silicona</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>0</v>
@@ -2893,57 +2875,55 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1125121096</v>
-      </c>
-      <c r="B68" t="inlineStr"/>
+        <v>1133985544</v>
+      </c>
+      <c r="B68" t="n">
+        <v>10660.5</v>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>375</v>
       </c>
-      <c r="E68" t="n">
-        <v>276</v>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>33.756</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>LCD</t>
-        </is>
-      </c>
+        <v>52.479</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>822208885</v>
+        <v>1112712822</v>
       </c>
       <c r="B69" t="n">
-        <v>3385</v>
+        <v>6444.5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Daza</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>HiFuture</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>240</v>
+      </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>19.208</v>
+        <v>34.163</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
@@ -2961,31 +2941,31 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>929882638</v>
+        <v>925835044</v>
       </c>
       <c r="B70" t="n">
-        <v>10660.5</v>
+        <v>3385</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
+          <t>Ruffo</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>82.5</v>
+        <v>185</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>28.829</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
@@ -2994,22 +2974,22 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>886371185</v>
+        <v>932546799</v>
       </c>
       <c r="B71" t="n">
-        <v>7995</v>
+        <v>5012.5</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Kingwear</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>40.64</v>
+        <v>30.099</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
@@ -3017,70 +2997,68 @@
           <t>Silicona</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.054</v>
+      </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1133985544</v>
+        <v>877038180</v>
       </c>
       <c r="B72" t="n">
-        <v>10660.5</v>
+        <v>5012.5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>375</v>
-      </c>
+          <t>Nictom</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>52.479</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
+        <v>19.335</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1112712822</v>
+        <v>918271785</v>
       </c>
       <c r="B73" t="n">
-        <v>6455</v>
+        <v>1495</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HiFuture</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>240</v>
-      </c>
+          <t>PSP_BAND</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>33.756</v>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>1</v>
       </c>
@@ -3091,32 +3069,30 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>925835044</v>
+        <v>848888616</v>
       </c>
       <c r="B74" t="n">
-        <v>3385</v>
+        <v>7930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ruffo</t>
+          <t>HDT8</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>43.22499999999999</v>
+        <v>30.099</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+          <t>Acero inoxidable/Silicona</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>0</v>
@@ -3124,22 +3100,20 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>932546799</v>
+        <v>1122543689</v>
       </c>
       <c r="B75" t="n">
-        <v>5012.5</v>
+        <v>3385</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kingwear</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>296</v>
-      </c>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>28.829</v>
+        <v>34.163</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
@@ -3151,7 +3125,7 @@
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0535</v>
+        <v>0.0247</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3159,26 +3133,24 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>877038180</v>
+        <v>1124107776</v>
       </c>
       <c r="B76" t="n">
-        <v>5012.5</v>
+        <v>10660.5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nictom</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Doogee</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>296</v>
+      </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
+        <v>34.163</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Silicona</t>
@@ -3189,24 +3161,26 @@
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>918271785</v>
+        <v>1136446808</v>
       </c>
       <c r="B77" t="n">
-        <v>1495</v>
+        <v>6444.5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PSP_BAND</t>
+          <t>Level Up</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>19.335</v>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
@@ -3219,30 +3193,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>848888616</v>
+        <v>692168723</v>
       </c>
       <c r="B78" t="n">
-        <v>7995</v>
+        <v>6444.5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HDT8</t>
+          <t>Kingwear</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>28.829</v>
+        <v>34.163</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Acero inoxidable/Silicona</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Silicona</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>0</v>
@@ -3250,20 +3226,20 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1122543689</v>
+        <v>918660631</v>
       </c>
       <c r="B79" t="n">
-        <v>3385</v>
+        <v>5012.5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>33.756</v>
+        <v>40.64</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
@@ -3274,40 +3250,32 @@
       <c r="I79" t="n">
         <v>1</v>
       </c>
-      <c r="J79" t="n">
-        <v>0.0275</v>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1124467536</v>
+        <v>899860978</v>
       </c>
       <c r="B80" t="n">
-        <v>7995</v>
+        <v>5012.5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Colmi</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>185</v>
-      </c>
-      <c r="E80" t="n">
-        <v>120</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>LCD TFT</t>
-        </is>
-      </c>
+          <t>Rohs</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>34.163</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -3315,32 +3283,32 @@
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1124107776</v>
+        <v>935014675</v>
       </c>
       <c r="B81" t="n">
-        <v>10660.5</v>
+        <v>7930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Doogee</t>
+          <t>Microwear</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>1ra Cuero/TPU - 2da Silicona negra</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -3348,59 +3316,65 @@
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1136446808</v>
+        <v>1116357643</v>
       </c>
       <c r="B82" t="n">
-        <v>6455</v>
+        <v>7930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Level Up</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>ISANFIT</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>185</v>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>19.208</v>
+        <v>30.099</v>
       </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1ra Metal - 2da Silicona</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>692168723</v>
+        <v>1113287659</v>
       </c>
       <c r="B83" t="n">
-        <v>6455</v>
+        <v>17689.5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kingwear</t>
+          <t>HiFuture</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -3413,20 +3387,22 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>918660631</v>
+        <v>1127906765</v>
       </c>
       <c r="B84" t="n">
-        <v>5012.5</v>
+        <v>10660.5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>375</v>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>40.64</v>
+        <v>34.163</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
@@ -3435,54 +3411,56 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>899860978</v>
+        <v>884556384</v>
       </c>
       <c r="B85" t="n">
-        <v>5012.5</v>
+        <v>3385</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rohs</t>
+          <t>Veryfit</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>33.756</v>
+        <v>19.335</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>935014675</v>
+        <v>1109687348</v>
       </c>
       <c r="B86" t="n">
-        <v>7995</v>
+        <v>5012.5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Microwear</t>
+          <t>Phull</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3490,32 +3468,34 @@
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>33.756</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1ra Cuero/TPU - 2da Silicona negra</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I86" t="n">
         <v>1</v>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1116357643</v>
+        <v>1135320848</v>
       </c>
       <c r="B87" t="n">
-        <v>7995</v>
+        <v>5012.5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ISANFIT</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3523,12 +3503,12 @@
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>33.756</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1ra Metal - 2da Silicona</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -3541,22 +3521,22 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1113287659</v>
+        <v>1120667658</v>
       </c>
       <c r="B88" t="n">
-        <v>17689.5</v>
+        <v>6444.5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HiFuture</t>
+          <t>Haxly</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>33.756</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
@@ -3569,34 +3549,26 @@
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1127906765</v>
+        <v>930491860</v>
       </c>
       <c r="B89" t="n">
-        <v>10660.5</v>
+        <v>1495</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>375</v>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="n">
-        <v>33.756</v>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -3607,55 +3579,55 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>884556384</v>
+        <v>790644541</v>
       </c>
       <c r="B90" t="n">
-        <v>3385</v>
+        <v>6444.5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Veryfit</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>19.208</v>
+        <v>30.099</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Cuero Genuino</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0275</v>
+        <v>0.0384</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1109687348</v>
+        <v>1106294913</v>
       </c>
       <c r="B91" t="n">
-        <v>5012.5</v>
+        <v>1495</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phull</t>
+          <t>Belmotec</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>185</v>
+        <v>82.5</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>43.22499999999999</v>
+        <v>52.479</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
@@ -3664,34 +3636,30 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0.0275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1135320848</v>
+        <v>1127614056</v>
       </c>
       <c r="B92" t="n">
-        <v>5012.5</v>
+        <v>1495</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="n">
-        <v>43.22499999999999</v>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
@@ -3699,99 +3667,107 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1120667658</v>
+        <v>1121025951</v>
       </c>
       <c r="B93" t="n">
-        <v>6455</v>
+        <v>5012.5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Haxly</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>185</v>
-      </c>
+          <t>Soul</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>37.211</v>
+        <v>34.163</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>930491860</v>
+        <v>712525200</v>
       </c>
       <c r="B94" t="n">
-        <v>1495</v>
+        <v>7930</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Integra</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>240</v>
+      </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>37.33799999999999</v>
+      </c>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>790644541</v>
+        <v>1132727262</v>
       </c>
       <c r="B95" t="n">
-        <v>6455</v>
+        <v>10660.5</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>240</v>
+      </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>28.829</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Cuero Genuino</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0399</v>
+        <v>0.054</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -3799,22 +3775,20 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1106294913</v>
+        <v>1139080671</v>
       </c>
       <c r="B96" t="n">
         <v>1495</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belmotec</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>82.5</v>
-      </c>
+          <t>Uprint</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>52.479</v>
+        <v>19.335</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
@@ -3832,21 +3806,21 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1127614056</v>
+        <v>1112931448</v>
       </c>
       <c r="B97" t="n">
-        <v>1495</v>
+        <v>17689.5</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>142</v>
-      </c>
+          <t>HiFuture</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>40.64</v>
+      </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
@@ -3858,34 +3832,36 @@
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1121025951</v>
+        <v>1124096467</v>
       </c>
       <c r="B98" t="n">
-        <v>5012.5</v>
+        <v>3385</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Soul</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>WICKPRO</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>82.5</v>
+      </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>33.756</v>
+        <v>19.335</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Plástico</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
@@ -3894,22 +3870,24 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>712525200</v>
+        <v>1128039769</v>
       </c>
       <c r="B99" t="n">
-        <v>7995</v>
+        <v>3385</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Integra</t>
+          <t>Netmak</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>240</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="E99" t="n">
+        <v>56</v>
+      </c>
       <c r="F99" t="n">
-        <v>37.211</v>
+        <v>34.163</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
@@ -3918,7 +3896,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
@@ -3927,55 +3905,47 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1132727262</v>
+        <v>904381316</v>
       </c>
       <c r="B100" t="n">
-        <v>10660.5</v>
+        <v>3385</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mistral</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>240</v>
-      </c>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>43.22499999999999</v>
+        <v>19.335</v>
       </c>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0.0535</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1139080671</v>
+        <v>1135493747</v>
       </c>
       <c r="B101" t="n">
-        <v>1495</v>
+        <v>3385</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Uprint</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>28.829</v>
+        <v>34.163</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
@@ -3988,25 +3958,25 @@
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1112931448</v>
+        <v>1127578475</v>
       </c>
       <c r="B102" t="n">
-        <v>17689.5</v>
+        <v>10660.5</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HiFuture</t>
+          <t>ONCELULAR2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>40.64</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
@@ -4019,19 +3989,19 @@
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1124096467</v>
+        <v>1108103077</v>
       </c>
       <c r="B103" t="n">
-        <v>3385</v>
+        <v>6444.5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WICKPRO</t>
+          <t>T-Go</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4039,42 +4009,42 @@
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
+        <v>19.335</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>Rosa / negra</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1128039769</v>
+        <v>1102402604</v>
       </c>
       <c r="B104" t="n">
-        <v>3385</v>
+        <v>5012.5</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netmak</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>142</v>
-      </c>
-      <c r="E104" t="n">
-        <v>120</v>
-      </c>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>33.756</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
@@ -4087,53 +4057,63 @@
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>904381316</v>
+        <v>897968783</v>
       </c>
       <c r="B105" t="n">
-        <v>3385</v>
+        <v>17689.5</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Kingwear</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>185</v>
+      </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+        <v>30.099</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Acero inoxidable</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.0384</v>
+      </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1135493747</v>
+        <v>925402929</v>
       </c>
       <c r="B106" t="n">
-        <v>3385</v>
+        <v>1495</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="n">
-        <v>33.756</v>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
@@ -4141,7 +4121,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
@@ -4150,20 +4130,22 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1127578475</v>
+        <v>1124419501</v>
       </c>
       <c r="B107" t="n">
-        <v>10660.5</v>
+        <v>7930</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ONCELULAR2</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>296</v>
+      </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>43.22499999999999</v>
+        <v>30.099</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
@@ -4172,7 +4154,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
@@ -4181,126 +4163,108 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1108103077</v>
+        <v>925704016</v>
       </c>
       <c r="B108" t="n">
-        <v>6455</v>
+        <v>3385</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>T-Go</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>82.5</v>
-      </c>
+          <t>JAZAK</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>LCD</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Rosa / negra</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1102402604</v>
+        <v>1122358418</v>
       </c>
       <c r="B109" t="n">
-        <v>5012.5</v>
+        <v>1495</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>LCS</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>82.5</v>
+      </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>43.22499999999999</v>
+        <v>19.335</v>
       </c>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>897968783</v>
+        <v>1134504848</v>
       </c>
       <c r="B110" t="n">
-        <v>17689.5</v>
+        <v>10660.5</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kingwear</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>185</v>
-      </c>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>28.829</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>TFT</t>
-        </is>
-      </c>
+        <v>43.22499999999999</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I110" t="n">
         <v>1</v>
       </c>
-      <c r="J110" t="n">
-        <v>0.0399</v>
-      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>925402929</v>
+        <v>1127902407</v>
       </c>
       <c r="B111" t="n">
-        <v>1495</v>
+        <v>10660.5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Haylou</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>240</v>
+      </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>30.099</v>
+      </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
@@ -4317,80 +4281,92 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1124419501</v>
-      </c>
-      <c r="B112" t="n">
-        <v>7995</v>
-      </c>
+        <v>903963153</v>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>296</v>
-      </c>
-      <c r="E112" t="inlineStr"/>
+          <t>Amazfit</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>288</v>
+      </c>
       <c r="F112" t="n">
-        <v>33.756</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
+        <v>34.163</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>925704016</v>
+        <v>930314427</v>
       </c>
       <c r="B113" t="n">
-        <v>3385</v>
+        <v>6444.5</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JAZAK</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>Kospet</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>185</v>
+      </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>37.33799999999999</v>
+      </c>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I113" t="n">
         <v>1</v>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>0.054</v>
+      </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1122358418</v>
+        <v>1141242030</v>
       </c>
       <c r="B114" t="n">
-        <v>1495</v>
+        <v>17689.5</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LCS</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>82.5</v>
+        <v>185</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>19.208</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
@@ -4399,25 +4375,27 @@
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1134504848</v>
+        <v>1129804339</v>
       </c>
       <c r="B115" t="n">
-        <v>10660.5</v>
+        <v>17689.5</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>185</v>
+      </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
-        <v>43.22499999999999</v>
+        <v>52.479</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
@@ -4430,28 +4408,22 @@
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1127902407</v>
-      </c>
-      <c r="B116" t="n">
-        <v>10660.5</v>
-      </c>
+        <v>1127740413</v>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Haylou</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>240</v>
-      </c>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="n">
-        <v>28.829</v>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
@@ -4459,7 +4431,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
@@ -4468,29 +4440,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>920152079</v>
-      </c>
-      <c r="B117" t="inlineStr"/>
+        <v>932503270</v>
+      </c>
+      <c r="B117" t="n">
+        <v>17689.5</v>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="n">
-        <v>120</v>
-      </c>
+          <t>Tressa</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>142</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>28.829</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+        <v>37.33799999999999</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -4498,54 +4468,52 @@
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>903963153</v>
-      </c>
-      <c r="B118" t="inlineStr"/>
+        <v>1140110031</v>
+      </c>
+      <c r="B118" t="n">
+        <v>6444.5</v>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Amazfit</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="n">
-        <v>276</v>
-      </c>
+          <t>BlueStar</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>185</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>37.211</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
+        <v>30.099</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>930314427</v>
+        <v>1140039402</v>
       </c>
       <c r="B119" t="n">
-        <v>6455</v>
+        <v>7930</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>WickPro</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4553,7 +4521,7 @@
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>37.211</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
@@ -4564,78 +4532,80 @@
       <c r="I119" t="n">
         <v>1</v>
       </c>
-      <c r="J119" t="n">
-        <v>0.0535</v>
-      </c>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1141242030</v>
+        <v>1138045378</v>
       </c>
       <c r="B120" t="n">
-        <v>17689.5</v>
+        <v>1495</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Huawei</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>185</v>
-      </c>
+          <t>Nictom</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="n">
-        <v>37.211</v>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Silicona</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1129804339</v>
+        <v>1108117596</v>
       </c>
       <c r="B121" t="n">
-        <v>17689.5</v>
+        <v>6444.5</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>T-Go</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>185</v>
-      </c>
-      <c r="E121" t="inlineStr"/>
+        <v>82.5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>288</v>
+      </c>
       <c r="F121" t="n">
-        <v>52.479</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
+        <v>19.335</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>1</v>
-      </c>
+          <t>TPU</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1127740413</v>
+        <v>1127728096</v>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
@@ -4645,7 +4615,9 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>52.479</v>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
@@ -4662,27 +4634,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>932503270</v>
+        <v>1102095082</v>
       </c>
       <c r="B123" t="n">
-        <v>17689.5</v>
+        <v>7930</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tressa</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>37.211</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Caucho</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -4695,27 +4667,25 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1140110031</v>
+        <v>906887097</v>
       </c>
       <c r="B124" t="n">
-        <v>6455</v>
+        <v>3385</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BlueStar</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>185</v>
-      </c>
+          <t>Suono</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Plástico</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -4723,19 +4693,19 @@
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1140039402</v>
+        <v>1102086547</v>
       </c>
       <c r="B125" t="n">
-        <v>7995</v>
+        <v>7930</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WickPro</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4743,7 +4713,7 @@
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>43.22499999999999</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
@@ -4761,19 +4731,21 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1138045378</v>
+        <v>1121038437</v>
       </c>
       <c r="B126" t="n">
-        <v>1495</v>
+        <v>3385</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Nictom</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>19.335</v>
+      </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
@@ -4781,45 +4753,39 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.054</v>
+      </c>
       <c r="K126" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1108117596</v>
+        <v>1129897442</v>
       </c>
       <c r="B127" t="n">
-        <v>6455</v>
+        <v>17689.5</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>T-Go</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="E127" t="n">
-        <v>276</v>
-      </c>
-      <c r="F127" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>LCD</t>
-        </is>
-      </c>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>TPU</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>Resina</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>1</v>
@@ -4827,27 +4793,31 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1127728096</v>
-      </c>
-      <c r="B128" t="inlineStr"/>
+        <v>1120641152</v>
+      </c>
+      <c r="B128" t="n">
+        <v>17689.5</v>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>SLA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>185</v>
+      </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>52.479</v>
+        <v>30.099</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
@@ -4856,58 +4826,62 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1102095082</v>
+        <v>1104970649</v>
       </c>
       <c r="B129" t="n">
-        <v>7995</v>
+        <v>10660.5</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Kospet</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
-        <v>37.211</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I129" t="n">
         <v>1</v>
       </c>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>0.0384</v>
+      </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>906887097</v>
+        <v>1137529813</v>
       </c>
       <c r="B130" t="n">
-        <v>3385</v>
+        <v>6444.5</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Suono</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Kanji</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>375</v>
+      </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
-        <v>33.756</v>
+        <v>19.335</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -4915,19 +4889,19 @@
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1102086547</v>
+        <v>897929203</v>
       </c>
       <c r="B131" t="n">
-        <v>7995</v>
+        <v>3385</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4935,7 +4909,7 @@
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>37.211</v>
+        <v>34.163</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
@@ -4944,29 +4918,33 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="K131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1121038437</v>
+        <v>931065158</v>
       </c>
       <c r="B132" t="n">
-        <v>3385</v>
+        <v>17689.5</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="n">
+        <v>296</v>
+      </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
-        <v>19.208</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
@@ -4975,34 +4953,36 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0.0535</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1129897442</v>
+        <v>1138943749</v>
       </c>
       <c r="B133" t="n">
-        <v>17689.5</v>
+        <v>3385</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mistral</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>X8</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>240</v>
+      </c>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>43.22499999999999</v>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Resina</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -5010,32 +4990,30 @@
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1120641152</v>
+        <v>872253400</v>
       </c>
       <c r="B134" t="n">
         <v>17689.5</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SLA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>185</v>
-      </c>
+          <t>LEZAYA</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -5048,82 +5026,80 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1104970649</v>
+        <v>1131163540</v>
       </c>
       <c r="B135" t="n">
-        <v>10660.5</v>
+        <v>17689.5</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>Tressa</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
-        <v>43.22499999999999</v>
+        <v>30.099</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Caucho</t>
         </is>
       </c>
       <c r="I135" t="n">
         <v>1</v>
       </c>
-      <c r="J135" t="n">
-        <v>0.0399</v>
-      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1137529813</v>
+        <v>1120444842</v>
       </c>
       <c r="B136" t="n">
-        <v>6455</v>
+        <v>17689.5</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kanji</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>375</v>
+        <v>185</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
-        <v>19.208</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>897929203</v>
+        <v>1102096932</v>
       </c>
       <c r="B137" t="n">
-        <v>3385</v>
+        <v>10660.5</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5131,7 +5107,7 @@
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
-        <v>33.756</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
@@ -5140,33 +5116,29 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0.0275</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>931065158</v>
+        <v>1127833359</v>
       </c>
       <c r="B138" t="n">
-        <v>17689.5</v>
+        <v>10660.5</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>296</v>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
-        <v>43.22499999999999</v>
+        <v>34.163</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
@@ -5175,7 +5147,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
@@ -5184,22 +5156,20 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1138943749</v>
+        <v>878394448</v>
       </c>
       <c r="B139" t="n">
         <v>3385</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>X8</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>240</v>
-      </c>
+          <t>Soul</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
-        <v>43.22499999999999</v>
+        <v>19.335</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
@@ -5207,9 +5177,7 @@
           <t>Silicona</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>1</v>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="n">
         <v>0</v>
@@ -5217,20 +5185,20 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>872253400</v>
+        <v>1137450477</v>
       </c>
       <c r="B140" t="n">
-        <v>17689.5</v>
+        <v>1495</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LEZAYA</t>
+          <t>Reloj Smartband M6</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
-        <v>33.756</v>
+        <v>52.479</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
@@ -5238,9 +5206,7 @@
           <t>Silicona</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>1</v>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
         <v>0</v>
@@ -5248,220 +5214,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1131163540</v>
+        <v>896351181</v>
       </c>
       <c r="B141" t="n">
-        <v>17689.5</v>
+        <v>7930</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tressa</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>240</v>
-      </c>
+          <t>SMART WATCH BRACELET</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>33.756</v>
+        <v>34.163</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>1120444842</v>
-      </c>
-      <c r="B142" t="n">
-        <v>17689.5</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Solana</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>185</v>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="n">
-        <v>43.22499999999999</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>TPU</t>
-        </is>
-      </c>
-      <c r="I142" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>1102096932</v>
-      </c>
-      <c r="B143" t="n">
-        <v>10660.5</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Stone</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>185</v>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="n">
-        <v>37.211</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I143" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>1127833359</v>
-      </c>
-      <c r="B144" t="n">
-        <v>10660.5</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="n">
-        <v>33.756</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I144" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>878394448</v>
-      </c>
-      <c r="B145" t="n">
-        <v>3385</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Soul</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="n">
-        <v>19.208</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>1137450477</v>
-      </c>
-      <c r="B146" t="n">
-        <v>1495</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Reloj Smartband M6</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="n">
-        <v>52.479</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>896351181</v>
-      </c>
-      <c r="B147" t="n">
-        <v>6455</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>SMART WATCH BRACELET</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="n">
-        <v>33.756</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="n">
         <v>1</v>
       </c>
     </row>
